--- a/data/raw-data/traits/Metatraits.xlsx
+++ b/data/raw-data/traits/Metatraits.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Traits" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="386">
   <si>
     <t>database</t>
   </si>
@@ -624,7 +624,7 @@
     <t>SLA</t>
   </si>
   <si>
-    <t>SLA.mm2.mg-1</t>
+    <t>SLA_mm2.mg-1</t>
   </si>
   <si>
     <t xml:space="preserve">Specific leaf area</t>
@@ -1023,7 +1023,7 @@
     <t>UV_reflection_periphery</t>
   </si>
   <si>
-    <t>Flower.UV.reflectanceperiphery</t>
+    <t>Flower.UV.reflectance.periphery</t>
   </si>
   <si>
     <t xml:space="preserve">Refers to the ability of the outer parts of the flower (petals/lobes) to reflect ultraviolet (UV) light. T</t>
@@ -1044,9 +1044,6 @@
     <t>Geographic_range</t>
   </si>
   <si>
-    <t>At_Vinedivers</t>
-  </si>
-  <si>
     <t>private</t>
   </si>
   <si>
@@ -1104,18 +1101,6 @@
     <t>Europe</t>
   </si>
   <si>
-    <t>Dcube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hintze, C., Heydel, F., Hoppe, C., Cunze, S., König, A., &amp; Tackenberg, O. (2013). D3: the dispersal and diaspore database–baseline data and statistics on seed dispersal. Perspectives in Plant Ecology, Evolution and Systematics, 15(3), 180-192.</t>
-  </si>
-  <si>
-    <t>https://ars.els-cdn.com/content/image/1-s2.0-S1433831913000218-mmc1.txt</t>
-  </si>
-  <si>
-    <t>1-s2.0-S1433831913000218-mmc1.txt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fitter, A. H. and Peat, H. J., 1994, The Ecological Flora Database, J. Ecol., 82, 415-425.</t>
   </si>
   <si>
@@ -1146,21 +1131,6 @@
     <t>https://gift.uni-goettingen.de/home</t>
   </si>
   <si>
-    <t>Groot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guerrero-Ramirez N, Mommer L, Freschet GT, Iversen CM, ... , Weigelt A. 2021. Global Root Traits (GRooT) Database. Global Ecology and Biogeography 30(1): 25-37</t>
-  </si>
-  <si>
-    <t>https://groot-database.github.io/GRooT/</t>
-  </si>
-  <si>
-    <t>GRooTAggregateSpeciesVersion.csv</t>
-  </si>
-  <si>
-    <t>Hodgson_2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hodgson, J., Jones, G., Charles, M., Stroud, E., ... &amp; Bogaard, A. (2023). A functional trait database of arable weeds from Eurasia and North Africa.</t>
   </si>
   <si>
@@ -1168,42 +1138,6 @@
   </si>
   <si>
     <t>Functional+trait+database+of+arable+weeds+from+Eurasia+and+North+Africa.xlsx</t>
-  </si>
-  <si>
-    <t>Lososova_2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lososová Z., Axmanová I., Chytrý M., Midolo G., ... &amp; Thuiller W. (2023). Seed dispersal distance classes and dispersal modes for the European flora. Global Ecology and Biogeography.</t>
-  </si>
-  <si>
-    <t>https://files.ibot.cas.cz/cevs/downloads/floraveg/Lososova_et_al_2023_Dispersal_version2_2024-06-14.xlsx</t>
-  </si>
-  <si>
-    <t>Lososova_et_al_2023_Dispersal_version2_2024-06-14.xlsx</t>
-  </si>
-  <si>
-    <t>TraitSpVignes.xls</t>
-  </si>
-  <si>
-    <t>Tichy_2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tichý, L., Axmanová, I., Dengler, J., Guarino, R., Jansen, F., Midolo, G., ... &amp; Chytrý, M. (2023). Ellenberg‐type indicator values for European vascular plant species. Journal of Vegetation Science, 34(1), e13168.</t>
-  </si>
-  <si>
-    <t>https://files.ibot.cas.cz/cevs/downloads/floraveg/Indicator_values_Tichy_et_al%202022-11-29.xlsx</t>
-  </si>
-  <si>
-    <t>Ellenberg_Indicator_values_Tichy_2022.xlsx</t>
-  </si>
-  <si>
-    <t>Yvoz_ValPol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeurs polliniques estimees.csv</t>
-  </si>
-  <si>
-    <t>Ladouceur_2019</t>
   </si>
   <si>
     <r>
@@ -1250,12 +1184,45 @@
   <si>
     <t>jvs12784-sup-0005-supinfo.csv</t>
   </si>
+  <si>
+    <t xml:space="preserve">Lososová Z., Axmanová I., Chytrý M., Midolo G., ... &amp; Thuiller W. (2023). Seed dispersal distance classes and dispersal modes for the European flora. Global Ecology and Biogeography.</t>
+  </si>
+  <si>
+    <t>https://files.ibot.cas.cz/cevs/downloads/floraveg/Lososova_et_al_2023_Dispersal_version2_2024-06-14.xlsx</t>
+  </si>
+  <si>
+    <t>Lososova_et_al_2023_Dispersal_version2_2024-06-14.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midolo, G., Herben, T., Axmanová, I., Marcenò, C., ... &amp; Chytrý, M. (2023). Disturbance indicator values for European plants. Global Ecology and Biogeography, 32(1), 24-34.</t>
+  </si>
+  <si>
+    <t>https://files.ibot.cas.cz/cevs/downloads/floraveg/disturbance_indicator_values.xlsx</t>
+  </si>
+  <si>
+    <t>disturbance_indicator_values_Midolo_2023.xlsx</t>
+  </si>
+  <si>
+    <t>TraitSpVignes.xls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tichý, L., Axmanová, I., Dengler, J., Guarino, R., Jansen, F., Midolo, G., ... &amp; Chytrý, M. (2023). Ellenberg‐type indicator values for European vascular plant species. Journal of Vegetation Science, 34(1), e13168.</t>
+  </si>
+  <si>
+    <t>https://files.ibot.cas.cz/cevs/downloads/floraveg/Indicator_values_Tichy_et_al%202022-11-29.xlsx</t>
+  </si>
+  <si>
+    <t>Ellenberg_Indicator_values_Tichy_2022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valeurs polliniques estimees.csv</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1300,6 +1267,17 @@
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1336,7 +1314,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1359,9 +1337,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
@@ -1370,11 +1345,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1383,20 +1358,28 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="8" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="9" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="10" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="9" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3529,7 +3512,7 @@
       <c r="B72" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D72" t="s">
@@ -3713,10 +3696,10 @@
       <c r="A80" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="9" t="s">
         <v>251</v>
       </c>
       <c r="D80" s="8" t="s">
@@ -3734,10 +3717,10 @@
       <c r="A81" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="9" t="s">
         <v>254</v>
       </c>
       <c r="D81" s="8" t="s">
@@ -3755,10 +3738,10 @@
       <c r="A82" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="10" t="s">
         <v>256</v>
       </c>
       <c r="D82" s="8" t="s">
@@ -3774,10 +3757,10 @@
       <c r="A83" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="9" t="s">
         <v>258</v>
       </c>
       <c r="D83" s="8" t="s">
@@ -3793,10 +3776,10 @@
       <c r="A84" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="9" t="s">
         <v>260</v>
       </c>
       <c r="D84" s="8" t="s">
@@ -3812,10 +3795,10 @@
       <c r="A85" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="9" t="s">
         <v>262</v>
       </c>
       <c r="D85" s="8" t="s">
@@ -3833,10 +3816,10 @@
       <c r="A86" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="9" t="s">
         <v>264</v>
       </c>
       <c r="D86" s="8" t="s">
@@ -4351,324 +4334,308 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.8515625"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="13.8515625"/>
     <col customWidth="1" min="2" max="2" width="82.7109375"/>
     <col customWidth="1" min="3" max="4" width="19.00390625"/>
     <col customWidth="1" min="5" max="5" width="17.421875"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5">
+      <c r="A3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" ht="42.75">
+      <c r="A4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5">
+      <c r="A5" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5">
+      <c r="A6" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5">
+      <c r="A7" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5">
+      <c r="A8" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" ht="28.5">
+      <c r="A9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10" ht="28.5">
+      <c r="A10" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" ht="28.5">
+      <c r="A11" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" ht="42.75">
+      <c r="A12" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" ht="28.5">
+      <c r="A13" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75">
+      <c r="A14" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>379</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="15" ht="15">
+      <c r="A15" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3" ht="28.5">
-      <c r="A3" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="C15" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" ht="42.75">
-      <c r="A4" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5">
-      <c r="A5" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>354</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5">
-      <c r="A6" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="D6" s="17" t="s">
+    </row>
+    <row r="16" ht="42.75">
+      <c r="A16" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="7" ht="42.75">
-      <c r="A7" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5">
-      <c r="A8" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5">
-      <c r="A9" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="10" ht="28.5">
-      <c r="A10" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="11" ht="28.5">
-      <c r="A11" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" ht="28.5">
-      <c r="A12" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="13" ht="28.5">
-      <c r="A13" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="14" ht="28.5">
-      <c r="A14" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="D14" s="17" t="s">
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="16" ht="42.75">
-      <c r="A16" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="17" ht="15">
-      <c r="A17" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="18" ht="42.75">
-      <c r="A18" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>395</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>359</v>
+      <c r="E17" s="17" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D17" columnSort="0">
+  <sortState ref="A2:E17" columnSort="0">
     <sortCondition sortBy="value" descending="0" ref="A2:A17"/>
   </sortState>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C18"/>
+    <hyperlink r:id="rId1" ref="C12"/>
+    <hyperlink r:id="rId2" ref="C14"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
